--- a/랜드로버_models.xlsx
+++ b/랜드로버_models.xlsx
@@ -11,7 +11,7 @@
     <sheet name="안내" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'랜드로버 트랜스폰더 DB'!$A$1:$P$156</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'랜드로버 트랜스폰더 DB'!$A$1:$P$140</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -521,7 +521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P156"/>
+  <dimension ref="A1:P140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7366,7 +7366,11 @@
         </is>
       </c>
       <c r="I102" s="9" t="inlineStr"/>
-      <c r="J102" s="9" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>HU101</t>
+        </is>
+      </c>
       <c r="K102" s="9" t="inlineStr"/>
       <c r="L102" s="9" t="inlineStr"/>
       <c r="M102" s="9" t="inlineStr"/>
@@ -7377,7 +7381,7 @@
       </c>
       <c r="O102" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover Sport L461 2023–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, 뉴시스(3세대 공개·국내 출시)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover Sport L461 2023–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, abkeys·CLK(JLR 스마트키 비상키 HU101), 뉴시스(3세대 공개·국내 출시)</t>
         </is>
       </c>
       <c r="P102" s="9" t="inlineStr"/>
@@ -7424,7 +7428,11 @@
         </is>
       </c>
       <c r="I103" s="9" t="inlineStr"/>
-      <c r="J103" s="9" t="inlineStr"/>
+      <c r="J103" s="9" t="inlineStr">
+        <is>
+          <t>HU101</t>
+        </is>
+      </c>
       <c r="K103" s="9" t="inlineStr"/>
       <c r="L103" s="9" t="inlineStr"/>
       <c r="M103" s="9" t="inlineStr"/>
@@ -7435,7 +7443,7 @@
       </c>
       <c r="O103" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover Sport L461 2023–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, 뉴시스(3세대 공개·국내 출시)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover Sport L461 2023–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, abkeys·CLK(JLR 스마트키 비상키 HU101), 뉴시스(3세대 공개·국내 출시)</t>
         </is>
       </c>
       <c r="P103" s="9" t="inlineStr"/>
@@ -7482,7 +7490,11 @@
         </is>
       </c>
       <c r="I104" s="9" t="inlineStr"/>
-      <c r="J104" s="9" t="inlineStr"/>
+      <c r="J104" s="9" t="inlineStr">
+        <is>
+          <t>HU101</t>
+        </is>
+      </c>
       <c r="K104" s="9" t="inlineStr"/>
       <c r="L104" s="9" t="inlineStr"/>
       <c r="M104" s="9" t="inlineStr"/>
@@ -7493,7 +7505,7 @@
       </c>
       <c r="O104" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover Sport L461 2023–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, 뉴시스(3세대 공개·국내 출시)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover Sport L461 2023–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, abkeys·CLK(JLR 스마트키 비상키 HU101), 뉴시스(3세대 공개·국내 출시)</t>
         </is>
       </c>
       <c r="P104" s="9" t="inlineStr"/>
@@ -7540,7 +7552,11 @@
         </is>
       </c>
       <c r="I105" s="9" t="inlineStr"/>
-      <c r="J105" s="9" t="inlineStr"/>
+      <c r="J105" s="9" t="inlineStr">
+        <is>
+          <t>HU101</t>
+        </is>
+      </c>
       <c r="K105" s="9" t="inlineStr"/>
       <c r="L105" s="9" t="inlineStr"/>
       <c r="M105" s="9" t="inlineStr"/>
@@ -7551,7 +7567,7 @@
       </c>
       <c r="O105" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover Sport L461 2023–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, 뉴시스(3세대 공개·국내 출시)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover Sport L461 2023–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, abkeys·CLK(JLR 스마트키 비상키 HU101), 뉴시스(3세대 공개·국내 출시)</t>
         </is>
       </c>
       <c r="P105" s="9" t="inlineStr"/>
@@ -7564,22 +7580,22 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>디펜더 (신형, L663)</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F106" s="3" t="inlineStr">
@@ -7587,40 +7603,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G106" s="4" t="inlineStr">
-        <is>
-          <t>ID44(PCF7935)</t>
+      <c r="G106" s="9" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H106" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I106" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I106" s="9" t="inlineStr">
+        <is>
+          <t>LR116570[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K106" s="9" t="inlineStr"/>
-      <c r="L106" s="9" t="inlineStr"/>
+      <c r="L106" s="9" t="inlineStr">
+        <is>
+          <t>LR116874[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M106" s="9" t="inlineStr"/>
-      <c r="N106" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈</t>
+      <c r="N106" s="9" t="inlineStr">
+        <is>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O106" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 1999–2003 PCF7935 ID44, Lucas 10AS)</t>
-        </is>
-      </c>
-      <c r="P106" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P106" s="9" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="9" t="inlineStr">
@@ -7630,22 +7650,22 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>디펜더 (신형, L663)</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -7653,40 +7673,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>ID44(PCF7935)</t>
+      <c r="G107" s="9" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H107" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I107" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>LR116570[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K107" s="9" t="inlineStr"/>
-      <c r="L107" s="9" t="inlineStr"/>
+      <c r="L107" s="9" t="inlineStr">
+        <is>
+          <t>LR116874[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M107" s="9" t="inlineStr"/>
-      <c r="N107" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈</t>
+      <c r="N107" s="9" t="inlineStr">
+        <is>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O107" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 1999–2003 PCF7935 ID44, Lucas 10AS)</t>
-        </is>
-      </c>
-      <c r="P107" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P107" s="9" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="9" t="inlineStr">
@@ -7696,22 +7720,22 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>디펜더 (신형, L663)</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F108" s="3" t="inlineStr">
@@ -7719,40 +7743,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>ID44(PCF7935)</t>
+      <c r="G108" s="9" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H108" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I108" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I108" s="9" t="inlineStr">
+        <is>
+          <t>LR116570[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K108" s="9" t="inlineStr"/>
-      <c r="L108" s="9" t="inlineStr"/>
+      <c r="L108" s="9" t="inlineStr">
+        <is>
+          <t>LR116874[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M108" s="9" t="inlineStr"/>
-      <c r="N108" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈</t>
+      <c r="N108" s="9" t="inlineStr">
+        <is>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O108" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 1999–2003 PCF7935 ID44, Lucas 10AS)</t>
-        </is>
-      </c>
-      <c r="P108" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P108" s="9" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="9" t="inlineStr">
@@ -7762,22 +7790,22 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>디펜더 (신형, L663)</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -7785,40 +7813,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>ID44(PCF7935)</t>
+      <c r="G109" s="9" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H109" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I109" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>LR116570[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K109" s="9" t="inlineStr"/>
-      <c r="L109" s="9" t="inlineStr"/>
+      <c r="L109" s="9" t="inlineStr">
+        <is>
+          <t>LR116874[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M109" s="9" t="inlineStr"/>
-      <c r="N109" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈</t>
+      <c r="N109" s="9" t="inlineStr">
+        <is>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O109" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 1999–2003 PCF7935 ID44, Lucas 10AS)</t>
-        </is>
-      </c>
-      <c r="P109" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P109" s="9" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="9" t="inlineStr">
@@ -7828,22 +7860,22 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>디펜더 (신형, L663)</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F110" s="3" t="inlineStr">
@@ -7851,40 +7883,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G110" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G110" s="9" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H110" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I110" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>LR116570[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K110" s="9" t="inlineStr"/>
-      <c r="L110" s="9" t="inlineStr"/>
+      <c r="L110" s="9" t="inlineStr">
+        <is>
+          <t>LR116874[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M110" s="9" t="inlineStr"/>
-      <c r="N110" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈</t>
+      <c r="N110" s="9" t="inlineStr">
+        <is>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O110" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2003–2013 PCF7936 ID46, YWX101220·YWX101230)</t>
-        </is>
-      </c>
-      <c r="P110" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P110" s="9" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="9" t="inlineStr">
@@ -7894,22 +7930,22 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>디펜더 (신형, L663)</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -7917,40 +7953,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G111" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H111" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I111" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>LR116570[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K111" s="9" t="inlineStr"/>
-      <c r="L111" s="9" t="inlineStr"/>
+      <c r="L111" s="9" t="inlineStr">
+        <is>
+          <t>LR116874[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M111" s="9" t="inlineStr"/>
-      <c r="N111" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈</t>
+      <c r="N111" s="9" t="inlineStr">
+        <is>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O111" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2003–2013 PCF7936 ID46, YWX101220·YWX101230)</t>
-        </is>
-      </c>
-      <c r="P111" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P111" s="9" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="9" t="inlineStr">
@@ -7960,22 +8000,22 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>디펜더 (신형, L663)</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F112" s="3" t="inlineStr">
@@ -7983,40 +8023,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G112" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G112" s="9" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H112" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I112" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I112" s="9" t="inlineStr">
+        <is>
+          <t>LR116570[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K112" s="9" t="inlineStr"/>
-      <c r="L112" s="9" t="inlineStr"/>
+      <c r="L112" s="9" t="inlineStr">
+        <is>
+          <t>LR116874[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M112" s="9" t="inlineStr"/>
-      <c r="N112" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈</t>
+      <c r="N112" s="9" t="inlineStr">
+        <is>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O112" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2003–2013 PCF7936 ID46, YWX101220·YWX101230)</t>
-        </is>
-      </c>
-      <c r="P112" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+        </is>
+      </c>
+      <c r="P112" s="9" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="9" t="inlineStr">
@@ -8026,12 +8070,12 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>레인지로버 (2세대, P38A)</t>
         </is>
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="D113" s="3" t="inlineStr">
@@ -8070,17 +8114,17 @@
       <c r="M113" s="9" t="inlineStr"/>
       <c r="N113" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈</t>
+          <t>BeCM</t>
         </is>
       </c>
       <c r="O113" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2003–2013 PCF7936 ID46, YWX101220·YWX101230)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover P38A 1998–2002 PCF7936 ID46, BeCM 패시브 이모빌라이저)</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
+          <t>P38A 국내 판매 연식 자료 없음(1990년대 인치케이프·BMW 딜러 수입 기록만)</t>
         </is>
       </c>
     </row>
@@ -8092,12 +8136,12 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>레인지로버 (2세대, P38A)</t>
         </is>
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2001(단종)</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -8136,17 +8180,17 @@
       <c r="M114" s="9" t="inlineStr"/>
       <c r="N114" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈</t>
+          <t>BeCM</t>
         </is>
       </c>
       <c r="O114" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2003–2013 PCF7936 ID46, YWX101220·YWX101230)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover P38A 1998–2002 PCF7936 ID46, BeCM 패시브 이모빌라이저)</t>
         </is>
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
+          <t>P38A 국내 판매 연식 자료 없음(1990년대 인치케이프·BMW 딜러 수입 기록만)</t>
         </is>
       </c>
     </row>
@@ -8158,12 +8202,12 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -8181,9 +8225,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>ID44(PCF7935)</t>
         </is>
       </c>
       <c r="H115" s="9" t="inlineStr">
@@ -8194,27 +8238,23 @@
       <c r="I115" s="9" t="inlineStr"/>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K115" s="9" t="inlineStr"/>
       <c r="L115" s="9" t="inlineStr"/>
       <c r="M115" s="9" t="inlineStr"/>
-      <c r="N115" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈</t>
+      <c r="N115" s="9" t="inlineStr">
+        <is>
+          <t>EWS3</t>
         </is>
       </c>
       <c r="O115" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2003–2013 PCF7936 ID46, YWX101220·YWX101230)</t>
-        </is>
-      </c>
-      <c r="P115" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2002–2005 PCF7935 ID44, BMW 계열 EWS3), abkeys(순정 레인지로버 보그 2002-2008 리모컨 일체형 키 433MHz HU92)</t>
+        </is>
+      </c>
+      <c r="P115" s="9" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="9" t="inlineStr">
@@ -8224,12 +8264,12 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -8247,9 +8287,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G116" s="9" t="inlineStr">
+        <is>
+          <t>ID44(PCF7935)</t>
         </is>
       </c>
       <c r="H116" s="9" t="inlineStr">
@@ -8260,27 +8300,23 @@
       <c r="I116" s="9" t="inlineStr"/>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K116" s="9" t="inlineStr"/>
       <c r="L116" s="9" t="inlineStr"/>
       <c r="M116" s="9" t="inlineStr"/>
-      <c r="N116" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈</t>
+      <c r="N116" s="9" t="inlineStr">
+        <is>
+          <t>EWS3</t>
         </is>
       </c>
       <c r="O116" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2003–2013 PCF7936 ID46, YWX101220·YWX101230)</t>
-        </is>
-      </c>
-      <c r="P116" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2002–2005 PCF7935 ID44, BMW 계열 EWS3), abkeys(순정 레인지로버 보그 2002-2008 리모컨 일체형 키 433MHz HU92)</t>
+        </is>
+      </c>
+      <c r="P116" s="9" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="9" t="inlineStr">
@@ -8290,12 +8326,12 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -8313,9 +8349,9 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>ID44(PCF7935)</t>
         </is>
       </c>
       <c r="H117" s="9" t="inlineStr">
@@ -8326,27 +8362,23 @@
       <c r="I117" s="9" t="inlineStr"/>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K117" s="9" t="inlineStr"/>
       <c r="L117" s="9" t="inlineStr"/>
       <c r="M117" s="9" t="inlineStr"/>
-      <c r="N117" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 모듈</t>
+      <c r="N117" s="9" t="inlineStr">
+        <is>
+          <t>EWS3</t>
         </is>
       </c>
       <c r="O117" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2003–2013 PCF7936 ID46, YWX101220·YWX101230)</t>
-        </is>
-      </c>
-      <c r="P117" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2002–2005 PCF7935 ID44, BMW 계열 EWS3), abkeys(순정 레인지로버 보그 2002-2008 리모컨 일체형 키 433MHz HU92)</t>
+        </is>
+      </c>
+      <c r="P117" s="9" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="9" t="inlineStr">
@@ -8356,12 +8388,12 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D118" s="3" t="inlineStr">
@@ -8381,7 +8413,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)</t>
+          <t>ID44(PCF7935)[전기 생산]</t>
         </is>
       </c>
       <c r="H118" s="9" t="inlineStr">
@@ -8392,7 +8424,7 @@
       <c r="I118" s="9" t="inlineStr"/>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU92</t>
         </is>
       </c>
       <c r="K118" s="9" t="inlineStr"/>
@@ -8400,17 +8432,17 @@
       <c r="M118" s="9" t="inlineStr"/>
       <c r="N118" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈</t>
+          <t>EWS3[전기 생산]</t>
         </is>
       </c>
       <c r="O118" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2003–2013 PCF7936 ID46, YWX101220·YWX101230)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
+          <t>EWS3(ID44)→ID46 전환 시점 자료 없음</t>
         </is>
       </c>
     </row>
@@ -8422,12 +8454,12 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="D119" s="3" t="inlineStr">
@@ -8447,18 +8479,18 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)</t>
+          <t>ID46(PCF7936)[후기 생산]</t>
         </is>
       </c>
       <c r="H119" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I119" s="9" t="inlineStr"/>
       <c r="J119" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K119" s="9" t="inlineStr"/>
@@ -8466,17 +8498,17 @@
       <c r="M119" s="9" t="inlineStr"/>
       <c r="N119" s="4" t="inlineStr">
         <is>
-          <t>이모빌라이저 모듈</t>
+          <t>이모빌라이저 박스(9S12DG128)[후기 생산]</t>
         </is>
       </c>
       <c r="O119" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2003–2013 PCF7936 ID46, YWX101220·YWX101230)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
+          <t>EWS3(ID44)→ID46 전환 시점 자료 없음</t>
         </is>
       </c>
     </row>
@@ -8488,22 +8520,22 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F120" s="3" t="inlineStr">
@@ -8511,14 +8543,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G120" s="4" t="inlineStr">
-        <is>
-          <t>ID49(PCF7953P)</t>
+      <c r="G120" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H120" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I120" s="9" t="inlineStr"/>
@@ -8530,21 +8562,17 @@
       <c r="K120" s="9" t="inlineStr"/>
       <c r="L120" s="9" t="inlineStr"/>
       <c r="M120" s="9" t="inlineStr"/>
-      <c r="N120" s="4" t="inlineStr">
-        <is>
-          <t>KVM</t>
+      <c r="N120" s="9" t="inlineStr">
+        <is>
+          <t>이모빌라이저 박스(9S12DG128)</t>
         </is>
       </c>
       <c r="O120" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2014–2016 PCF7953P ID49)</t>
-        </is>
-      </c>
-      <c r="P120" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
+        </is>
+      </c>
+      <c r="P120" s="9" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="9" t="inlineStr">
@@ -8554,22 +8582,22 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (구형)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>2015(단종)</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E121" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -8577,14 +8605,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G121" s="4" t="inlineStr">
-        <is>
-          <t>ID49(PCF7953P)</t>
+      <c r="G121" s="9" t="inlineStr">
+        <is>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H121" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
+          <t>폴딩키</t>
         </is>
       </c>
       <c r="I121" s="9" t="inlineStr"/>
@@ -8596,21 +8624,17 @@
       <c r="K121" s="9" t="inlineStr"/>
       <c r="L121" s="9" t="inlineStr"/>
       <c r="M121" s="9" t="inlineStr"/>
-      <c r="N121" s="4" t="inlineStr">
-        <is>
-          <t>KVM</t>
+      <c r="N121" s="9" t="inlineStr">
+        <is>
+          <t>이모빌라이저 박스(9S12DG128)</t>
         </is>
       </c>
       <c r="O121" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L316 2014–2016 PCF7953P ID49)</t>
-        </is>
-      </c>
-      <c r="P121" s="4" t="inlineStr">
-        <is>
-          <t>국내 정식 판매 기록 없음 — 해외 사양 기준</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
+        </is>
+      </c>
+      <c r="P121" s="9" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="9" t="inlineStr">
@@ -8620,22 +8644,22 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (신형, L663)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F122" s="3" t="inlineStr">
@@ -8645,39 +8669,31 @@
       </c>
       <c r="G122" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H122" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I122" s="9" t="inlineStr">
-        <is>
-          <t>LR116570[해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="I122" s="9" t="inlineStr"/>
       <c r="J122" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
         </is>
       </c>
       <c r="K122" s="9" t="inlineStr"/>
-      <c r="L122" s="9" t="inlineStr">
-        <is>
-          <t>LR116874[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L122" s="9" t="inlineStr"/>
       <c r="M122" s="9" t="inlineStr"/>
       <c r="N122" s="9" t="inlineStr">
         <is>
-          <t>RFA</t>
+          <t>이모빌라이저 박스(9S12DG128)</t>
         </is>
       </c>
       <c r="O122" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
         </is>
       </c>
       <c r="P122" s="9" t="inlineStr"/>
@@ -8690,22 +8706,22 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (신형, L663)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -8715,39 +8731,31 @@
       </c>
       <c r="G123" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46(PCF7936)</t>
         </is>
       </c>
       <c r="H123" s="9" t="inlineStr">
         <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>LR116570[해외 공용 품번]</t>
-        </is>
-      </c>
+          <t>폴딩키</t>
+        </is>
+      </c>
+      <c r="I123" s="9" t="inlineStr"/>
       <c r="J123" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
         </is>
       </c>
       <c r="K123" s="9" t="inlineStr"/>
-      <c r="L123" s="9" t="inlineStr">
-        <is>
-          <t>LR116874[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L123" s="9" t="inlineStr"/>
       <c r="M123" s="9" t="inlineStr"/>
       <c r="N123" s="9" t="inlineStr">
         <is>
-          <t>RFA</t>
+          <t>이모빌라이저 박스(9S12DG128)</t>
         </is>
       </c>
       <c r="O123" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
         </is>
       </c>
       <c r="P123" s="9" t="inlineStr"/>
@@ -8760,22 +8768,22 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (신형, L663)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F124" s="3" t="inlineStr">
@@ -8785,7 +8793,7 @@
       </c>
       <c r="G124" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46(PCF7953A)</t>
         </is>
       </c>
       <c r="H124" s="9" t="inlineStr">
@@ -8793,11 +8801,7 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I124" s="9" t="inlineStr">
-        <is>
-          <t>LR116570[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I124" s="9" t="inlineStr"/>
       <c r="J124" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
@@ -8806,18 +8810,18 @@
       <c r="K124" s="9" t="inlineStr"/>
       <c r="L124" s="9" t="inlineStr">
         <is>
-          <t>LR116874[해외 공용 품번]</t>
+          <t>LR020366[해외 공용 품번], LR032796[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M124" s="9" t="inlineStr"/>
       <c r="N124" s="9" t="inlineStr">
         <is>
-          <t>RFA</t>
+          <t>KVM</t>
         </is>
       </c>
       <c r="O124" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2009–2011 PCF7953A ID46, LR020365·LR020366·LR032796·AH42-15K601-AF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
         </is>
       </c>
       <c r="P124" s="9" t="inlineStr"/>
@@ -8830,22 +8834,22 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (신형, L663)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -8855,7 +8859,7 @@
       </c>
       <c r="G125" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID46(PCF7953A)</t>
         </is>
       </c>
       <c r="H125" s="9" t="inlineStr">
@@ -8863,11 +8867,7 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I125" s="9" t="inlineStr">
-        <is>
-          <t>LR116570[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I125" s="9" t="inlineStr"/>
       <c r="J125" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
@@ -8876,18 +8876,18 @@
       <c r="K125" s="9" t="inlineStr"/>
       <c r="L125" s="9" t="inlineStr">
         <is>
-          <t>LR116874[해외 공용 품번]</t>
+          <t>LR020366[해외 공용 품번], LR032796[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M125" s="9" t="inlineStr"/>
       <c r="N125" s="9" t="inlineStr">
         <is>
-          <t>RFA</t>
+          <t>KVM</t>
         </is>
       </c>
       <c r="O125" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2009–2011 PCF7953A ID46, LR020365·LR020366·LR032796·AH42-15K601-AF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
         </is>
       </c>
       <c r="P125" s="9" t="inlineStr"/>
@@ -8900,12 +8900,12 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (신형, L663)</t>
+          <t>레인지로버 (3세대, L322)</t>
         </is>
       </c>
       <c r="C126" s="9" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2012(단종)</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -8925,7 +8925,7 @@
       </c>
       <c r="G126" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H126" s="9" t="inlineStr">
@@ -8933,11 +8933,7 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I126" s="9" t="inlineStr">
-        <is>
-          <t>LR116570[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I126" s="9" t="inlineStr"/>
       <c r="J126" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
@@ -8946,18 +8942,18 @@
       <c r="K126" s="9" t="inlineStr"/>
       <c r="L126" s="9" t="inlineStr">
         <is>
-          <t>LR116874[해외 공용 품번]</t>
+          <t>LR087661[해외 공용 품번], LR087663[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M126" s="9" t="inlineStr"/>
       <c r="N126" s="9" t="inlineStr">
         <is>
-          <t>RFA</t>
+          <t>KVM</t>
         </is>
       </c>
       <c r="O126" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2012 PCF7953P ID49, LR087661·LR087663), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
         </is>
       </c>
       <c r="P126" s="9" t="inlineStr"/>
@@ -8970,12 +8966,12 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (신형, L663)</t>
+          <t>레인지로버 (4세대, L405)</t>
         </is>
       </c>
       <c r="C127" s="9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -8995,7 +8991,7 @@
       </c>
       <c r="G127" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H127" s="9" t="inlineStr">
@@ -9003,11 +8999,7 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I127" s="9" t="inlineStr">
-        <is>
-          <t>LR116570[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I127" s="9" t="inlineStr"/>
       <c r="J127" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
@@ -9016,18 +9008,18 @@
       <c r="K127" s="9" t="inlineStr"/>
       <c r="L127" s="9" t="inlineStr">
         <is>
-          <t>LR116874[해외 공용 품번]</t>
+          <t>LR087106[해외 공용 품번], LR087661[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M127" s="9" t="inlineStr"/>
       <c r="N127" s="9" t="inlineStr">
         <is>
-          <t>RFA</t>
+          <t>KVM, BCM</t>
         </is>
       </c>
       <c r="O127" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2013·2014–2017 PCF7953P ID49, LR087106·LR087661·LR087663, BJ32-15K601-DF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
         </is>
       </c>
       <c r="P127" s="9" t="inlineStr"/>
@@ -9040,12 +9032,12 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>디펜더 (신형, L663)</t>
+          <t>레인지로버 (4세대, L405)</t>
         </is>
       </c>
       <c r="C128" s="9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -9065,7 +9057,7 @@
       </c>
       <c r="G128" s="9" t="inlineStr">
         <is>
-          <t>ID49</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H128" s="9" t="inlineStr">
@@ -9073,11 +9065,7 @@
           <t>스마트키</t>
         </is>
       </c>
-      <c r="I128" s="9" t="inlineStr">
-        <is>
-          <t>LR116570[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="I128" s="9" t="inlineStr"/>
       <c r="J128" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
@@ -9086,18 +9074,18 @@
       <c r="K128" s="9" t="inlineStr"/>
       <c r="L128" s="9" t="inlineStr">
         <is>
-          <t>LR116874[해외 공용 품번]</t>
+          <t>LR087106[해외 공용 품번], LR087661[해외 공용 품번]</t>
         </is>
       </c>
       <c r="M128" s="9" t="inlineStr"/>
       <c r="N128" s="9" t="inlineStr">
         <is>
-          <t>RFA</t>
+          <t>KVM, BCM</t>
         </is>
       </c>
       <c r="O128" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Defender L663 2020–2026+ Hitag Pro ID49 NCF29, LR116874·LR133282·LR163588, K8D2 RFA), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+), 서울신문·탑라이더(신형 디펜더 2020.7 국내 출시)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2013·2014–2017 PCF7953P ID49, LR087106·LR087661·LR087663, BJ32-15K601-DF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
         </is>
       </c>
       <c r="P128" s="9" t="inlineStr"/>
@@ -9110,22 +9098,22 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (2세대, P38A)</t>
+          <t>레인지로버 (4세대, L405)</t>
         </is>
       </c>
       <c r="C129" s="9" t="inlineStr">
         <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -9133,40 +9121,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G129" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G129" s="9" t="inlineStr">
+        <is>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H129" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I129" s="9" t="inlineStr"/>
       <c r="J129" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K129" s="9" t="inlineStr"/>
-      <c r="L129" s="9" t="inlineStr"/>
+      <c r="L129" s="9" t="inlineStr">
+        <is>
+          <t>LR087106[해외 공용 품번], LR087661[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M129" s="9" t="inlineStr"/>
-      <c r="N129" s="4" t="inlineStr">
-        <is>
-          <t>BeCM</t>
+      <c r="N129" s="9" t="inlineStr">
+        <is>
+          <t>KVM, BCM</t>
         </is>
       </c>
       <c r="O129" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover P38A 1998–2002 PCF7936 ID46, BeCM 패시브 이모빌라이저)</t>
-        </is>
-      </c>
-      <c r="P129" s="4" t="inlineStr">
-        <is>
-          <t>P38A 국내 판매 연식 자료 없음(1990년대 인치케이프·BMW 딜러 수입 기록만)</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2013·2014–2017 PCF7953P ID49, LR087106·LR087661·LR087663, BJ32-15K601-DF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
+        </is>
+      </c>
+      <c r="P129" s="9" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="9" t="inlineStr">
@@ -9176,22 +9164,22 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (2세대, P38A)</t>
+          <t>레인지로버 (4세대, L405)</t>
         </is>
       </c>
       <c r="C130" s="9" t="inlineStr">
         <is>
-          <t>2001(단종)</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E130" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F130" s="3" t="inlineStr">
@@ -9199,40 +9187,40 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G130" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)</t>
+      <c r="G130" s="9" t="inlineStr">
+        <is>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H130" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I130" s="9" t="inlineStr"/>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>NE38</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K130" s="9" t="inlineStr"/>
-      <c r="L130" s="9" t="inlineStr"/>
+      <c r="L130" s="9" t="inlineStr">
+        <is>
+          <t>LR087106[해외 공용 품번], LR087661[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M130" s="9" t="inlineStr"/>
-      <c r="N130" s="4" t="inlineStr">
-        <is>
-          <t>BeCM</t>
+      <c r="N130" s="9" t="inlineStr">
+        <is>
+          <t>KVM, BCM</t>
         </is>
       </c>
       <c r="O130" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover P38A 1998–2002 PCF7936 ID46, BeCM 패시브 이모빌라이저)</t>
-        </is>
-      </c>
-      <c r="P130" s="4" t="inlineStr">
-        <is>
-          <t>P38A 국내 판매 연식 자료 없음(1990년대 인치케이프·BMW 딜러 수입 기록만)</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2013·2014–2017 PCF7953P ID49, LR087106·LR087661·LR087663, BJ32-15K601-DF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
+        </is>
+      </c>
+      <c r="P130" s="9" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="9" t="inlineStr">
@@ -9242,22 +9230,22 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (3세대, L322)</t>
+          <t>레인지로버 (4세대, L405)</t>
         </is>
       </c>
       <c r="C131" s="9" t="inlineStr">
         <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E131" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -9267,31 +9255,35 @@
       </c>
       <c r="G131" s="9" t="inlineStr">
         <is>
-          <t>ID44(PCF7935)</t>
+          <t>ID49(PCF7953P)</t>
         </is>
       </c>
       <c r="H131" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I131" s="9" t="inlineStr"/>
       <c r="J131" s="9" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K131" s="9" t="inlineStr"/>
-      <c r="L131" s="9" t="inlineStr"/>
+      <c r="L131" s="9" t="inlineStr">
+        <is>
+          <t>LR087106[해외 공용 품번], LR087661[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M131" s="9" t="inlineStr"/>
       <c r="N131" s="9" t="inlineStr">
         <is>
-          <t>EWS3</t>
+          <t>KVM, BCM</t>
         </is>
       </c>
       <c r="O131" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2002–2005 PCF7935 ID44, BMW 계열 EWS3), abkeys(순정 레인지로버 보그 2002-2008 리모컨 일체형 키 433MHz HU92)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2013·2014–2017 PCF7953P ID49, LR087106·LR087661·LR087663, BJ32-15K601-DF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
         </is>
       </c>
       <c r="P131" s="9" t="inlineStr"/>
@@ -9304,22 +9296,22 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (3세대, L322)</t>
+          <t>레인지로버 (4세대, L405)</t>
         </is>
       </c>
       <c r="C132" s="9" t="inlineStr">
         <is>
-          <t>2003</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E132" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F132" s="3" t="inlineStr">
@@ -9329,31 +9321,39 @@
       </c>
       <c r="G132" s="9" t="inlineStr">
         <is>
-          <t>ID44(PCF7935)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H132" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I132" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>LR116570[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K132" s="9" t="inlineStr"/>
-      <c r="L132" s="9" t="inlineStr"/>
+      <c r="L132" s="9" t="inlineStr">
+        <is>
+          <t>LR116874[해외 공용 품번], JK52-15K601-BG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M132" s="9" t="inlineStr"/>
       <c r="N132" s="9" t="inlineStr">
         <is>
-          <t>EWS3</t>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O132" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2002–2005 PCF7935 ID44, BMW 계열 EWS3), abkeys(순정 레인지로버 보그 2002-2008 리모컨 일체형 키 433MHz HU92)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2018–2021 Hitag Pro ID49 NCF29, LR116874·JK52-15K601-BG), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
         </is>
       </c>
       <c r="P132" s="9" t="inlineStr"/>
@@ -9366,22 +9366,22 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (3세대, L322)</t>
+          <t>레인지로버 (4세대, L405)</t>
         </is>
       </c>
       <c r="C133" s="9" t="inlineStr">
         <is>
-          <t>2004</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E133" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -9391,31 +9391,39 @@
       </c>
       <c r="G133" s="9" t="inlineStr">
         <is>
-          <t>ID44(PCF7935)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H133" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I133" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>LR116570[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J133" s="9" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K133" s="9" t="inlineStr"/>
-      <c r="L133" s="9" t="inlineStr"/>
+      <c r="L133" s="9" t="inlineStr">
+        <is>
+          <t>LR116874[해외 공용 품번], JK52-15K601-BG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M133" s="9" t="inlineStr"/>
       <c r="N133" s="9" t="inlineStr">
         <is>
-          <t>EWS3</t>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O133" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2002–2005 PCF7935 ID44, BMW 계열 EWS3), abkeys(순정 레인지로버 보그 2002-2008 리모컨 일체형 키 433MHz HU92)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2018–2021 Hitag Pro ID49 NCF29, LR116874·JK52-15K601-BG), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
         </is>
       </c>
       <c r="P133" s="9" t="inlineStr"/>
@@ -9428,22 +9436,22 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (3세대, L322)</t>
+          <t>레인지로버 (4세대, L405)</t>
         </is>
       </c>
       <c r="C134" s="9" t="inlineStr">
         <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E134" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F134" s="3" t="inlineStr">
@@ -9451,40 +9459,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G134" s="4" t="inlineStr">
-        <is>
-          <t>ID44(PCF7935)[전기 생산]</t>
+      <c r="G134" s="9" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H134" s="9" t="inlineStr">
         <is>
-          <t>막대키</t>
-        </is>
-      </c>
-      <c r="I134" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>LR116570[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J134" s="9" t="inlineStr">
         <is>
-          <t>HU92</t>
+          <t>HU101</t>
         </is>
       </c>
       <c r="K134" s="9" t="inlineStr"/>
-      <c r="L134" s="9" t="inlineStr"/>
+      <c r="L134" s="9" t="inlineStr">
+        <is>
+          <t>LR116874[해외 공용 품번], JK52-15K601-BG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M134" s="9" t="inlineStr"/>
-      <c r="N134" s="4" t="inlineStr">
-        <is>
-          <t>EWS3[전기 생산]</t>
+      <c r="N134" s="9" t="inlineStr">
+        <is>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O134" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
-        </is>
-      </c>
-      <c r="P134" s="4" t="inlineStr">
-        <is>
-          <t>EWS3(ID44)→ID46 전환 시점 자료 없음</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2018–2021 Hitag Pro ID49 NCF29, LR116874·JK52-15K601-BG), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
+        </is>
+      </c>
+      <c r="P134" s="9" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="9" t="inlineStr">
@@ -9494,22 +9506,22 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (3세대, L322)</t>
+          <t>레인지로버 (4세대, L405)</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2021(단종)</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -9517,40 +9529,44 @@
           <t>O</t>
         </is>
       </c>
-      <c r="G135" s="4" t="inlineStr">
-        <is>
-          <t>ID46(PCF7936)[후기 생산]</t>
+      <c r="G135" s="9" t="inlineStr">
+        <is>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H135" s="9" t="inlineStr">
         <is>
-          <t>폴딩키</t>
-        </is>
-      </c>
-      <c r="I135" s="9" t="inlineStr"/>
+          <t>스마트키</t>
+        </is>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>LR116570[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="J135" s="9" t="inlineStr">
         <is>
           <t>HU101</t>
         </is>
       </c>
       <c r="K135" s="9" t="inlineStr"/>
-      <c r="L135" s="9" t="inlineStr"/>
+      <c r="L135" s="9" t="inlineStr">
+        <is>
+          <t>LR116874[해외 공용 품번], JK52-15K601-BG[해외 공용 품번]</t>
+        </is>
+      </c>
       <c r="M135" s="9" t="inlineStr"/>
-      <c r="N135" s="4" t="inlineStr">
-        <is>
-          <t>이모빌라이저 박스(9S12DG128)[후기 생산]</t>
+      <c r="N135" s="9" t="inlineStr">
+        <is>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O135" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
-        </is>
-      </c>
-      <c r="P135" s="4" t="inlineStr">
-        <is>
-          <t>EWS3(ID44)→ID46 전환 시점 자료 없음</t>
-        </is>
-      </c>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2018–2021 Hitag Pro ID49 NCF29, LR116874·JK52-15K601-BG), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
+        </is>
+      </c>
+      <c r="P135" s="9" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="9" t="inlineStr">
@@ -9560,22 +9576,22 @@
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (3세대, L322)</t>
+          <t>레인지로버 (5세대, L460)</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>2006</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F136" s="3" t="inlineStr">
@@ -9585,12 +9601,12 @@
       </c>
       <c r="G136" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H136" s="9" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I136" s="9" t="inlineStr"/>
@@ -9604,12 +9620,12 @@
       <c r="M136" s="9" t="inlineStr"/>
       <c r="N136" s="9" t="inlineStr">
         <is>
-          <t>이모빌라이저 박스(9S12DG128)</t>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O136" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L460 2022–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, abkeys·CLK(JLR 스마트키 비상키 HU101)</t>
         </is>
       </c>
       <c r="P136" s="9" t="inlineStr"/>
@@ -9622,22 +9638,22 @@
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (3세대, L322)</t>
+          <t>레인지로버 (5세대, L460)</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -9647,12 +9663,12 @@
       </c>
       <c r="G137" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H137" s="9" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I137" s="9" t="inlineStr"/>
@@ -9666,12 +9682,12 @@
       <c r="M137" s="9" t="inlineStr"/>
       <c r="N137" s="9" t="inlineStr">
         <is>
-          <t>이모빌라이저 박스(9S12DG128)</t>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O137" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L460 2022–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, abkeys·CLK(JLR 스마트키 비상키 HU101)</t>
         </is>
       </c>
       <c r="P137" s="9" t="inlineStr"/>
@@ -9684,22 +9700,22 @@
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (3세대, L322)</t>
+          <t>레인지로버 (5세대, L460)</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>2008</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E138" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F138" s="3" t="inlineStr">
@@ -9709,12 +9725,12 @@
       </c>
       <c r="G138" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H138" s="9" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I138" s="9" t="inlineStr"/>
@@ -9728,12 +9744,12 @@
       <c r="M138" s="9" t="inlineStr"/>
       <c r="N138" s="9" t="inlineStr">
         <is>
-          <t>이모빌라이저 박스(9S12DG128)</t>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O138" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L460 2022–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, abkeys·CLK(JLR 스마트키 비상키 HU101)</t>
         </is>
       </c>
       <c r="P138" s="9" t="inlineStr"/>
@@ -9746,22 +9762,22 @@
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (3세대, L322)</t>
+          <t>레인지로버 (5세대, L460)</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E139" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -9771,12 +9787,12 @@
       </c>
       <c r="G139" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7936)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H139" s="9" t="inlineStr">
         <is>
-          <t>폴딩키</t>
+          <t>스마트키</t>
         </is>
       </c>
       <c r="I139" s="9" t="inlineStr"/>
@@ -9790,12 +9806,12 @@
       <c r="M139" s="9" t="inlineStr"/>
       <c r="N139" s="9" t="inlineStr">
         <is>
-          <t>이모빌라이저 박스(9S12DG128)</t>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O139" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2005–2009 PCF7936 ID46, 이모빌라이저 박스 9S12DG128, CWE500041SW·LR088260), abkeys(보그 2007-2010 플립키 433MHz PCF7936)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L460 2022–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, abkeys·CLK(JLR 스마트키 비상키 HU101)</t>
         </is>
       </c>
       <c r="P139" s="9" t="inlineStr"/>
@@ -9808,22 +9824,22 @@
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>레인지로버 (3세대, L322)</t>
+          <t>레인지로버 (5세대, L460)</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>2010</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E140" s="6" t="inlineStr">
+        <is>
+          <t>△</t>
         </is>
       </c>
       <c r="F140" s="3" t="inlineStr">
@@ -9833,7 +9849,7 @@
       </c>
       <c r="G140" s="9" t="inlineStr">
         <is>
-          <t>ID46(PCF7953A)</t>
+          <t>ID49</t>
         </is>
       </c>
       <c r="H140" s="9" t="inlineStr">
@@ -9848,1058 +9864,22 @@
         </is>
       </c>
       <c r="K140" s="9" t="inlineStr"/>
-      <c r="L140" s="9" t="inlineStr">
-        <is>
-          <t>LR020366[해외 공용 품번], LR032796[해외 공용 품번]</t>
-        </is>
-      </c>
+      <c r="L140" s="9" t="inlineStr"/>
       <c r="M140" s="9" t="inlineStr"/>
       <c r="N140" s="9" t="inlineStr">
         <is>
-          <t>KVM</t>
+          <t>RFA</t>
         </is>
       </c>
       <c r="O140" s="9" t="inlineStr">
         <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2009–2011 PCF7953A ID46, LR020365·LR020366·LR032796·AH42-15K601-AF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
+          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L460 2022–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨, abkeys·CLK(JLR 스마트키 비상키 HU101)</t>
         </is>
       </c>
       <c r="P140" s="9" t="inlineStr"/>
     </row>
-    <row r="141">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B141" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (3세대, L322)</t>
-        </is>
-      </c>
-      <c r="C141" s="9" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G141" s="9" t="inlineStr">
-        <is>
-          <t>ID46(PCF7953A)</t>
-        </is>
-      </c>
-      <c r="H141" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I141" s="9" t="inlineStr"/>
-      <c r="J141" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K141" s="9" t="inlineStr"/>
-      <c r="L141" s="9" t="inlineStr">
-        <is>
-          <t>LR020366[해외 공용 품번], LR032796[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M141" s="9" t="inlineStr"/>
-      <c r="N141" s="9" t="inlineStr">
-        <is>
-          <t>KVM</t>
-        </is>
-      </c>
-      <c r="O141" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2009–2011 PCF7953A ID46, LR020365·LR020366·LR032796·AH42-15K601-AF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
-        </is>
-      </c>
-      <c r="P141" s="9" t="inlineStr"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B142" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (3세대, L322)</t>
-        </is>
-      </c>
-      <c r="C142" s="9" t="inlineStr">
-        <is>
-          <t>2012(단종)</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F142" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G142" s="9" t="inlineStr">
-        <is>
-          <t>ID49(PCF7953P)</t>
-        </is>
-      </c>
-      <c r="H142" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I142" s="9" t="inlineStr"/>
-      <c r="J142" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K142" s="9" t="inlineStr"/>
-      <c r="L142" s="9" t="inlineStr">
-        <is>
-          <t>LR087661[해외 공용 품번], LR087663[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M142" s="9" t="inlineStr"/>
-      <c r="N142" s="9" t="inlineStr">
-        <is>
-          <t>KVM</t>
-        </is>
-      </c>
-      <c r="O142" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L322 2012 PCF7953P ID49, LR087661·LR087663), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
-        </is>
-      </c>
-      <c r="P142" s="9" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B143" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (4세대, L405)</t>
-        </is>
-      </c>
-      <c r="C143" s="9" t="inlineStr">
-        <is>
-          <t>2013</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E143" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G143" s="9" t="inlineStr">
-        <is>
-          <t>ID49(PCF7953P)</t>
-        </is>
-      </c>
-      <c r="H143" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I143" s="9" t="inlineStr"/>
-      <c r="J143" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K143" s="9" t="inlineStr"/>
-      <c r="L143" s="9" t="inlineStr">
-        <is>
-          <t>LR087106[해외 공용 품번], LR087661[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M143" s="9" t="inlineStr"/>
-      <c r="N143" s="9" t="inlineStr">
-        <is>
-          <t>KVM, BCM</t>
-        </is>
-      </c>
-      <c r="O143" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2013·2014–2017 PCF7953P ID49, LR087106·LR087661·LR087663, BJ32-15K601-DF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
-        </is>
-      </c>
-      <c r="P143" s="9" t="inlineStr"/>
-    </row>
-    <row r="144">
-      <c r="A144" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B144" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (4세대, L405)</t>
-        </is>
-      </c>
-      <c r="C144" s="9" t="inlineStr">
-        <is>
-          <t>2014</t>
-        </is>
-      </c>
-      <c r="D144" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G144" s="9" t="inlineStr">
-        <is>
-          <t>ID49(PCF7953P)</t>
-        </is>
-      </c>
-      <c r="H144" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I144" s="9" t="inlineStr"/>
-      <c r="J144" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K144" s="9" t="inlineStr"/>
-      <c r="L144" s="9" t="inlineStr">
-        <is>
-          <t>LR087106[해외 공용 품번], LR087661[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M144" s="9" t="inlineStr"/>
-      <c r="N144" s="9" t="inlineStr">
-        <is>
-          <t>KVM, BCM</t>
-        </is>
-      </c>
-      <c r="O144" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2013·2014–2017 PCF7953P ID49, LR087106·LR087661·LR087663, BJ32-15K601-DF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
-        </is>
-      </c>
-      <c r="P144" s="9" t="inlineStr"/>
-    </row>
-    <row r="145">
-      <c r="A145" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B145" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (4세대, L405)</t>
-        </is>
-      </c>
-      <c r="C145" s="9" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E145" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G145" s="9" t="inlineStr">
-        <is>
-          <t>ID49(PCF7953P)</t>
-        </is>
-      </c>
-      <c r="H145" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I145" s="9" t="inlineStr"/>
-      <c r="J145" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K145" s="9" t="inlineStr"/>
-      <c r="L145" s="9" t="inlineStr">
-        <is>
-          <t>LR087106[해외 공용 품번], LR087661[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M145" s="9" t="inlineStr"/>
-      <c r="N145" s="9" t="inlineStr">
-        <is>
-          <t>KVM, BCM</t>
-        </is>
-      </c>
-      <c r="O145" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2013·2014–2017 PCF7953P ID49, LR087106·LR087661·LR087663, BJ32-15K601-DF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
-        </is>
-      </c>
-      <c r="P145" s="9" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B146" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (4세대, L405)</t>
-        </is>
-      </c>
-      <c r="C146" s="9" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="D146" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G146" s="9" t="inlineStr">
-        <is>
-          <t>ID49(PCF7953P)</t>
-        </is>
-      </c>
-      <c r="H146" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I146" s="9" t="inlineStr"/>
-      <c r="J146" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K146" s="9" t="inlineStr"/>
-      <c r="L146" s="9" t="inlineStr">
-        <is>
-          <t>LR087106[해외 공용 품번], LR087661[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M146" s="9" t="inlineStr"/>
-      <c r="N146" s="9" t="inlineStr">
-        <is>
-          <t>KVM, BCM</t>
-        </is>
-      </c>
-      <c r="O146" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2013·2014–2017 PCF7953P ID49, LR087106·LR087661·LR087663, BJ32-15K601-DF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
-        </is>
-      </c>
-      <c r="P146" s="9" t="inlineStr"/>
-    </row>
-    <row r="147">
-      <c r="A147" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B147" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (4세대, L405)</t>
-        </is>
-      </c>
-      <c r="C147" s="9" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E147" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G147" s="9" t="inlineStr">
-        <is>
-          <t>ID49(PCF7953P)</t>
-        </is>
-      </c>
-      <c r="H147" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I147" s="9" t="inlineStr"/>
-      <c r="J147" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K147" s="9" t="inlineStr"/>
-      <c r="L147" s="9" t="inlineStr">
-        <is>
-          <t>LR087106[해외 공용 품번], LR087661[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M147" s="9" t="inlineStr"/>
-      <c r="N147" s="9" t="inlineStr">
-        <is>
-          <t>KVM, BCM</t>
-        </is>
-      </c>
-      <c r="O147" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2013·2014–2017 PCF7953P ID49, LR087106·LR087661·LR087663, BJ32-15K601-DF), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
-        </is>
-      </c>
-      <c r="P147" s="9" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B148" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (4세대, L405)</t>
-        </is>
-      </c>
-      <c r="C148" s="9" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="D148" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E148" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G148" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H148" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I148" s="9" t="inlineStr">
-        <is>
-          <t>LR116570[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J148" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K148" s="9" t="inlineStr"/>
-      <c r="L148" s="9" t="inlineStr">
-        <is>
-          <t>LR116874[해외 공용 품번], JK52-15K601-BG[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M148" s="9" t="inlineStr"/>
-      <c r="N148" s="9" t="inlineStr">
-        <is>
-          <t>RFA</t>
-        </is>
-      </c>
-      <c r="O148" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2018–2021 Hitag Pro ID49 NCF29, LR116874·JK52-15K601-BG), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
-        </is>
-      </c>
-      <c r="P148" s="9" t="inlineStr"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B149" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (4세대, L405)</t>
-        </is>
-      </c>
-      <c r="C149" s="9" t="inlineStr">
-        <is>
-          <t>2019</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E149" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G149" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H149" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I149" s="9" t="inlineStr">
-        <is>
-          <t>LR116570[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J149" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K149" s="9" t="inlineStr"/>
-      <c r="L149" s="9" t="inlineStr">
-        <is>
-          <t>LR116874[해외 공용 품번], JK52-15K601-BG[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M149" s="9" t="inlineStr"/>
-      <c r="N149" s="9" t="inlineStr">
-        <is>
-          <t>RFA</t>
-        </is>
-      </c>
-      <c r="O149" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2018–2021 Hitag Pro ID49 NCF29, LR116874·JK52-15K601-BG), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
-        </is>
-      </c>
-      <c r="P149" s="9" t="inlineStr"/>
-    </row>
-    <row r="150">
-      <c r="A150" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B150" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (4세대, L405)</t>
-        </is>
-      </c>
-      <c r="C150" s="9" t="inlineStr">
-        <is>
-          <t>2020</t>
-        </is>
-      </c>
-      <c r="D150" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E150" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G150" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H150" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I150" s="9" t="inlineStr">
-        <is>
-          <t>LR116570[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J150" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K150" s="9" t="inlineStr"/>
-      <c r="L150" s="9" t="inlineStr">
-        <is>
-          <t>LR116874[해외 공용 품번], JK52-15K601-BG[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M150" s="9" t="inlineStr"/>
-      <c r="N150" s="9" t="inlineStr">
-        <is>
-          <t>RFA</t>
-        </is>
-      </c>
-      <c r="O150" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2018–2021 Hitag Pro ID49 NCF29, LR116874·JK52-15K601-BG), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
-        </is>
-      </c>
-      <c r="P150" s="9" t="inlineStr"/>
-    </row>
-    <row r="151">
-      <c r="A151" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B151" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (4세대, L405)</t>
-        </is>
-      </c>
-      <c r="C151" s="9" t="inlineStr">
-        <is>
-          <t>2021(단종)</t>
-        </is>
-      </c>
-      <c r="D151" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E151" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G151" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H151" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I151" s="9" t="inlineStr">
-        <is>
-          <t>LR116570[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="J151" s="9" t="inlineStr">
-        <is>
-          <t>HU101</t>
-        </is>
-      </c>
-      <c r="K151" s="9" t="inlineStr"/>
-      <c r="L151" s="9" t="inlineStr">
-        <is>
-          <t>LR116874[해외 공용 품번], JK52-15K601-BG[해외 공용 품번]</t>
-        </is>
-      </c>
-      <c r="M151" s="9" t="inlineStr"/>
-      <c r="N151" s="9" t="inlineStr">
-        <is>
-          <t>RFA</t>
-        </is>
-      </c>
-      <c r="O151" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L405 2018–2021 Hitag Pro ID49 NCF29, LR116874·JK52-15K601-BG), jlridssddmongoose(LR020366·LR032796 433MHz, LR087106·LR087661·LR066836 433MHz Hitag Pro, LR116874 433/434MHz MY2015-2020+, JK52-15K601-BG 434MHz KVM), abkeys(순정 5E0U40247 433MHz PCF7953P ID49 레인지로버 스포츠·보그·이보크 2010+, 순정 JK52-15K601-BG 434MHz 2018+)</t>
-        </is>
-      </c>
-      <c r="P151" s="9" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B152" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (5세대, L460)</t>
-        </is>
-      </c>
-      <c r="C152" s="9" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="D152" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E152" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G152" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H152" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I152" s="9" t="inlineStr"/>
-      <c r="J152" s="9" t="inlineStr"/>
-      <c r="K152" s="9" t="inlineStr"/>
-      <c r="L152" s="9" t="inlineStr"/>
-      <c r="M152" s="9" t="inlineStr"/>
-      <c r="N152" s="9" t="inlineStr">
-        <is>
-          <t>RFA</t>
-        </is>
-      </c>
-      <c r="O152" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L460 2022–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨</t>
-        </is>
-      </c>
-      <c r="P152" s="9" t="inlineStr"/>
-    </row>
-    <row r="153">
-      <c r="A153" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B153" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (5세대, L460)</t>
-        </is>
-      </c>
-      <c r="C153" s="9" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D153" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E153" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G153" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H153" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I153" s="9" t="inlineStr"/>
-      <c r="J153" s="9" t="inlineStr"/>
-      <c r="K153" s="9" t="inlineStr"/>
-      <c r="L153" s="9" t="inlineStr"/>
-      <c r="M153" s="9" t="inlineStr"/>
-      <c r="N153" s="9" t="inlineStr">
-        <is>
-          <t>RFA</t>
-        </is>
-      </c>
-      <c r="O153" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L460 2022–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨</t>
-        </is>
-      </c>
-      <c r="P153" s="9" t="inlineStr"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B154" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (5세대, L460)</t>
-        </is>
-      </c>
-      <c r="C154" s="9" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="D154" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E154" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F154" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G154" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H154" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I154" s="9" t="inlineStr"/>
-      <c r="J154" s="9" t="inlineStr"/>
-      <c r="K154" s="9" t="inlineStr"/>
-      <c r="L154" s="9" t="inlineStr"/>
-      <c r="M154" s="9" t="inlineStr"/>
-      <c r="N154" s="9" t="inlineStr">
-        <is>
-          <t>RFA</t>
-        </is>
-      </c>
-      <c r="O154" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L460 2022–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨</t>
-        </is>
-      </c>
-      <c r="P154" s="9" t="inlineStr"/>
-    </row>
-    <row r="155">
-      <c r="A155" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B155" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (5세대, L460)</t>
-        </is>
-      </c>
-      <c r="C155" s="9" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="D155" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E155" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F155" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G155" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H155" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I155" s="9" t="inlineStr"/>
-      <c r="J155" s="9" t="inlineStr"/>
-      <c r="K155" s="9" t="inlineStr"/>
-      <c r="L155" s="9" t="inlineStr"/>
-      <c r="M155" s="9" t="inlineStr"/>
-      <c r="N155" s="9" t="inlineStr">
-        <is>
-          <t>RFA</t>
-        </is>
-      </c>
-      <c r="O155" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L460 2022–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨</t>
-        </is>
-      </c>
-      <c r="P155" s="9" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="9" t="inlineStr">
-        <is>
-          <t>랜드로버</t>
-        </is>
-      </c>
-      <c r="B156" s="9" t="inlineStr">
-        <is>
-          <t>레인지로버 (5세대, L460)</t>
-        </is>
-      </c>
-      <c r="C156" s="9" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="D156" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E156" s="6" t="inlineStr">
-        <is>
-          <t>△</t>
-        </is>
-      </c>
-      <c r="F156" s="3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="G156" s="9" t="inlineStr">
-        <is>
-          <t>ID49</t>
-        </is>
-      </c>
-      <c r="H156" s="9" t="inlineStr">
-        <is>
-          <t>스마트키</t>
-        </is>
-      </c>
-      <c r="I156" s="9" t="inlineStr"/>
-      <c r="J156" s="9" t="inlineStr"/>
-      <c r="K156" s="9" t="inlineStr"/>
-      <c r="L156" s="9" t="inlineStr"/>
-      <c r="M156" s="9" t="inlineStr"/>
-      <c r="N156" s="9" t="inlineStr">
-        <is>
-          <t>RFA</t>
-        </is>
-      </c>
-      <c r="O156" s="9" t="inlineStr">
-        <is>
-          <t>transpondery(Land Rover·Range Rover Catalog Range Rover L460 2022–2026+ Hitag Pro ID49 NCF29, LR163588·LR177484, K8D2 RFA·PEPS) — 433/434MHz 품번 확인 안 됨</t>
-        </is>
-      </c>
-      <c r="P156" s="9" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:P156"/>
+  <autoFilter ref="A1:P140"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11026,7 +10006,7 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>- 주황색: 추정이거나 자료가 서로 다른 값, 칩 전환 시점을 모르는 연식(전·후 2행), 또는 국내 정식 판매 기록이 없는 모델(구형 디펜더·P38A).</t>
+          <t>- 주황색: 추정이거나 자료가 서로 다른 값, 칩 전환 시점을 모르는 연식(전·후 2행).</t>
         </is>
       </c>
     </row>
@@ -11043,7 +10023,7 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>- 레인지로버 L405: 국내 2013년부터(L322 마지막 2012) / 구형 디펜더: 국내 정식 판매 기록을 찾지 못해 목록 연식대로 남기고 주황색 / 이보크 1세대 2011.12, 디스커버리 스포츠 2015.5, 벨라 2017.9, 신형 디펜더 2020.7 국내 출시.</t>
+          <t>- 레인지로버 L405: 국내 2013년부터(L322 마지막 2012) / 구형 디펜더(L316, 목록 1997-2015): 국내 정식 판매 기록이 없어 뺐습니다 / 이보크 1세대 2011.12, 디스커버리 스포츠 2015.5, 벨라 2017.9, 신형 디펜더 2020.7 국내 출시.</t>
         </is>
       </c>
     </row>
